--- a/apps/cliente/public/examples/file_time.xlsx
+++ b/apps/cliente/public/examples/file_time.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="18">
   <si>
     <t>employee_code</t>
   </si>
@@ -43,7 +43,28 @@
     <t>2026-09-03</t>
   </si>
   <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
     <t>EMP002</t>
+  </si>
+  <si>
+    <t>EMP004</t>
+  </si>
+  <si>
+    <t>EMP005</t>
+  </si>
+  <si>
+    <t>EMP006</t>
+  </si>
+  <si>
+    <t>EMP007</t>
+  </si>
+  <si>
+    <t>EMP008</t>
   </si>
 </sst>
 </file>
@@ -62,17 +83,12 @@
       <b/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -89,7 +105,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -494,7 +510,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -522,10 +538,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -542,10 +558,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -562,21 +578,601 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>9.5</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>9.5</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>9.5</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>9.5</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>8</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>9.5</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>9.5</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>8</v>
+      </c>
+      <c r="E34">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>8</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36">
         <v>0</v>
       </c>
     </row>
